--- a/doc/help_dialogs/Input_files/symbolic.xlsx
+++ b/doc/help_dialogs/Input_files/symbolic.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Symbolic Variables" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="178">
   <si>
     <t xml:space="preserve">SYMBOLIC VARIABLES</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t xml:space="preserve">Conditional. Evaluates to the value of the expression &lt;true-expr&gt; if the condition &lt;cond&gt; holds, otherwise to the value of the expression &lt;false-expr&gt;. The rules of Python are applied to decide if a value holds or not. Thus the boolean values "True" and "False" have the obvious semantic. Any number unequal to 0 evaluates to True and 0 evaluates to False. The value "None" is also evaluated to False.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bn:Note: If any of the referenced symbolic variables contained in a symbolic expression evaluates to the error value -1, the whole expression evaluates to -1. This can be prevented by surrounding the whole expression by regular brackets. Thus, with Y1 evaluating to -1, the expression "Y1 + 1" evaluates to -1, but "(Y1 + 1)" evaluates to 0.</t>
   </si>
   <si>
     <t xml:space="preserve">MATHEMATICAL FORMULAS</t>
@@ -572,7 +575,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -632,6 +635,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -689,7 +698,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -747,6 +756,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1362,7 +1375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.09"/>
@@ -1387,6 +1400,11 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1414,12 +1432,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>3</v>
@@ -1427,130 +1445,130 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1574,7 +1592,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1582,12 +1600,12 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2.71828182845904</v>
@@ -1595,7 +1613,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3.14159265358979</v>
@@ -1622,12 +1640,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1640,18 +1658,18 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
